--- a/Electrical/MainBoard/bom/digikeyV0.3.xlsx
+++ b/Electrical/MainBoard/bom/digikeyV0.3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satom\Desktop\Robot\Electrical\MainBoard\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E199D811-2817-463C-8D29-A28F61956B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC545E7-F174-4AE8-BD7C-FC83EADBAA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1123,7 +1123,7 @@
   <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="28.83984375" customWidth="1"/>
+    <col min="1" max="1" width="74.5234375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.20703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.89453125" customWidth="1"/>
   </cols>
